--- a/data/trans_dic/P20D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>53,19; 92,01</t>
+          <t>48,32; 91,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 55,93</t>
+          <t>10,88; 56,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,56; 71,8</t>
+          <t>37,34; 73,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,98; 79,33</t>
+          <t>26,64; 80,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,48; 81,55</t>
+          <t>32,4; 84,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,01; 76,12</t>
+          <t>36,33; 75,1</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,33; 86,55</t>
+          <t>38,8; 91,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,86; 75,63</t>
+          <t>13,81; 72,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,85; 77,54</t>
+          <t>37,8; 76,62</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,65; 92,12</t>
+          <t>57,44; 91,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,34; 48,14</t>
+          <t>15,43; 47,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,19; 68,53</t>
+          <t>42,25; 69,85</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,54; 80,67</t>
+          <t>58,73; 80,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,26; 53,16</t>
+          <t>25,77; 51,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,82; 64,54</t>
+          <t>47,09; 65,0</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo</t>
+          <t>Población que durante el ingreso estuvo acompañada por una mujer casi todo el tiempo (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8508; 14718</t>
+          <t>7730; 14570</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1422; 6460</t>
+          <t>1256; 6488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10071; 19779</t>
+          <t>10287; 20154</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2946; 9747</t>
+          <t>3274; 9862</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4357; 11288</t>
+          <t>4484; 11684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9931; 19887</t>
+          <t>9491; 19623</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5299; 12285</t>
+          <t>5508; 12926</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1106; 5275</t>
+          <t>963; 5083</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8225; 16415</t>
+          <t>8003; 16221</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12008; 18238</t>
+          <t>11372; 18163</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2681; 8413</t>
+          <t>2697; 8249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15727; 25544</t>
+          <t>15749; 26036</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36456; 50242</t>
+          <t>36577; 50411</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14084; 26495</t>
+          <t>12843; 25658</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53611; 72362</t>
+          <t>52796; 72878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20D_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P20D_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,32; 91,08</t>
+          <t>48,21; 89,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 56,17</t>
+          <t>12,28; 54,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,34; 73,16</t>
+          <t>35,85; 71,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 80,26</t>
+          <t>37,99; 85,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 84,42</t>
+          <t>34,92; 85,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 75,1</t>
+          <t>44,02; 78,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,8; 91,06</t>
+          <t>42,37; 92,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 72,87</t>
+          <t>15,45; 70,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,8; 76,62</t>
+          <t>42,03; 77,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,44; 91,74</t>
+          <t>56,6; 90,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,43; 47,2</t>
+          <t>17,84; 52,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,25; 69,85</t>
+          <t>40,77; 68,56</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>58,73; 80,95</t>
+          <t>61,02; 82,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,77; 51,48</t>
+          <t>29,01; 52,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47,09; 65,0</t>
+          <t>49,15; 64,92</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>16247</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7730; 14570</t>
+          <t>8028; 14919</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1256; 6488</t>
+          <t>1635; 7304</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10287; 20154</t>
+          <t>10744; 21298</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>19039</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3274; 9862</t>
+          <t>5946; 13375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4484; 11684</t>
+          <t>5397; 13147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9491; 19623</t>
+          <t>13693; 24471</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>14999</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5508; 12926</t>
+          <t>6546; 14268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>963; 5083</t>
+          <t>1419; 6502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8003; 16221</t>
+          <t>10354; 19064</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>22015</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11372; 18163</t>
+          <t>11575; 18403</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2697; 8249</t>
+          <t>3448; 10096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15749; 26036</t>
+          <t>16215; 27273</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>72300</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36577; 50411</t>
+          <t>41618; 56405</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12843; 25658</t>
+          <t>16616; 30142</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52796; 72878</t>
+          <t>61674; 81467</t>
         </is>
       </c>
     </row>
